--- a/nr-add-example/ig/ValueSet-VS-TRE-R74-ModeFixationTarifaire.xlsx
+++ b/nr-add-example/ig/ValueSet-VS-TRE-R74-ModeFixationTarifaire.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T08:11:19+00:00</t>
+    <t>2024-04-10T09:01:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-example/ig/ValueSet-VS-TRE-R74-ModeFixationTarifaire.xlsx
+++ b/nr-add-example/ig/ValueSet-VS-TRE-R74-ModeFixationTarifaire.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T09:01:28+00:00</t>
+    <t>2024-04-10T09:14:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-example/ig/ValueSet-VS-TRE-R74-ModeFixationTarifaire.xlsx
+++ b/nr-add-example/ig/ValueSet-VS-TRE-R74-ModeFixationTarifaire.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T09:14:30+00:00</t>
+    <t>2024-04-10T09:18:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
